--- a/bom/bom-production.xlsx
+++ b/bom/bom-production.xlsx
@@ -446,17 +446,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,7 +470,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev 0.3, 11 x 42 mm 4-layer, sourced from LCSC/JLCPCB. Quantities are per board.</t>
+          <t>Rev 0.3, 11 x 42 mm 4-layer. All parts sourced through JLCPCB assembly (LCSC part numbers). Quantities are per board.</t>
         </is>
       </c>
     </row>
@@ -507,10 +508,15 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>JLCPCB / LCSC part</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -542,7 +548,12 @@
           <t>C23733</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -570,7 +581,12 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -598,7 +614,12 @@
           <t>C23692971</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -626,7 +647,12 @@
           <t>C1525</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -654,7 +680,12 @@
           <t>C130723</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -682,7 +713,12 @@
           <t>C2988369</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -706,7 +742,8 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>bare solder pads - no part to order</t>
         </is>
@@ -738,7 +775,12 @@
           <t>C25905</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -766,7 +808,12 @@
           <t>C25765</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -794,7 +841,12 @@
           <t>C11702</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -822,7 +874,12 @@
           <t>C25900</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -850,7 +907,12 @@
           <t>C26083</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -874,7 +936,8 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -902,7 +965,8 @@
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -930,7 +994,8 @@
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -958,7 +1023,8 @@
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -999,6 +1065,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Mouser/DigiKey (consign)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>0 stock at JLC/LCSC - source from Mouser or DigiKey</t>
         </is>
@@ -1030,7 +1101,12 @@
           <t>C967633</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1058,7 +1134,12 @@
           <t>C424093</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1086,7 +1167,12 @@
           <t>C493453</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
     </row>
     <row r="25"/>
     <row r="26">
@@ -1099,21 +1185,28 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>U1 ISP1807-LR-RS has 0 stock at LCSC/JLCPCB: order from Mouser or DigiKey and consign it, or hand-place.</t>
+          <t>Order the PCB and assembly at jlcpcb.com; upload gerbers, BOM and CPL from production/output/.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>J2 battery pads and TP1/TP2/TP4/TP5 test pads are bare copper, nothing to order.</t>
+          <t>U1 ISP1807-LR-RS is the one exception: 0 stock at JLCPCB/LCSC. Buy it from Mouser or DigiKey and use JLC parts consignment, or hand-place it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>All passives are 0402 JLC basic parts.</t>
+          <t>J2 battery pads and TP1/TP2/TP4/TP5 test pads are bare copper, nothing to order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>All passives are 0402 JLC basic parts, no extended-part fee.</t>
         </is>
       </c>
     </row>

--- a/bom/bom-production.xlsx
+++ b/bom/bom-production.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +42,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -72,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -456,8 +465,8 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,10 +522,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Unit price (USD)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Line total (USD)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -548,12 +567,18 @@
           <t>C23733</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="6" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -581,12 +606,18 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -614,12 +645,18 @@
           <t>C23692971</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="6" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -647,12 +684,18 @@
           <t>C1525</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="6" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -680,12 +723,18 @@
           <t>C130723</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="6" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -713,12 +762,18 @@
           <t>C2988369</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="6" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -742,8 +797,8 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>bare solder pads - no part to order</t>
         </is>
@@ -775,12 +830,18 @@
           <t>C25905</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="6" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -808,12 +869,18 @@
           <t>C25765</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="6" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -841,12 +908,18 @@
           <t>C11702</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="6" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -874,12 +947,18 @@
           <t>C25900</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="6" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -907,12 +986,18 @@
           <t>C26083</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="6" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -936,8 +1021,8 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -965,8 +1050,8 @@
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -994,8 +1079,8 @@
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -1023,8 +1108,8 @@
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>bare pad - no part</t>
         </is>
@@ -1064,12 +1149,18 @@
           <t>C5264268</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="6" t="n">
+        <v>12.1151</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>12.1151</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Mouser/DigiKey (consign)</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>0 stock at JLC/LCSC - source from Mouser or DigiKey</t>
         </is>
@@ -1101,12 +1192,18 @@
           <t>C967633</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="6" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1134,12 +1231,18 @@
           <t>C424093</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="6" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1167,44 +1270,60 @@
           <t>C493453</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="6" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Parts total per board</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Ordering notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Order the PCB and assembly at jlcpcb.com; upload gerbers, BOM and CPL from production/output/.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>U1 ISP1807-LR-RS is the one exception: 0 stock at JLCPCB/LCSC. Buy it from Mouser or DigiKey and use JLC parts consignment, or hand-place it.</t>
+          <t>Order the PCB and assembly at jlcpcb.com; upload gerbers, BOM and CPL from production/output/.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>J2 battery pads and TP1/TP2/TP4/TP5 test pads are bare copper, nothing to order.</t>
+          <t>U1 ISP1807-LR-RS is the one exception: 0 stock at JLCPCB/LCSC. Buy it from Mouser or DigiKey and use JLC parts consignment, or hand-place it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>J2 battery pads and TP1/TP2/TP4/TP5 test pads are bare copper, nothing to order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>All passives are 0402 JLC basic parts, no extended-part fee.</t>
         </is>

--- a/bom/bom-production.xlsx
+++ b/bom/bom-production.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,26 +28,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Red Hat Display"/>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="00151515"/>
+      <sz val="15"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
       <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="006A6E73"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <name val="Red Hat Mono"/>
+      <color rgb="00151515"/>
+      <sz val="9"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
+      <color rgb="00151515"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Red Hat Display"/>
       <b val="1"/>
+      <color rgb="00151515"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Red Hat Display"/>
+      <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Red Hat Text"/>
+      <i val="1"/>
+      <color rgb="006A6E73"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,7 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
+        <fgColor rgb="00151515"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,26 +102,31 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D2D2D2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,15 +495,17 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="53" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,12 +518,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev 0.3, 11 x 42 mm 4-layer. All parts sourced through JLCPCB assembly (LCSC part numbers). Quantities are per board.</t>
+          <t>Rev 0.3, 11 x 42 mm 4-layer. Exported from KiCad, assembled at JLCPCB with LCSC parts. Quantities per board.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Reference</t>
@@ -517,7 +556,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>JLCPCB / LCSC part</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -544,24 +583,32 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>C2,C1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+          <t>C1,C2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>4u7</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CL05A475MP5NRNC</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>C23733</t>
@@ -573,129 +620,153 @@
       <c r="I5" s="7" t="n">
         <v>0.0464</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>C3,C4</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>CL05A105KA5NQNC</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>C52923</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="10" t="n">
         <v>0.012</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="11" t="n">
         <v>0.024</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>C5,C7,C8,C10</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CL05B104KO5NNNC</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>C1525</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>10u</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>CGA0402X5R106M6R3GT</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>TDK</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>C23692971</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H8" s="10" t="n">
         <v>0.0244</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I8" s="11" t="n">
         <v>0.0244</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>C10,C8,C5,C7</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>100n</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>C1525</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>JLCPCB</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -703,21 +774,29 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>GRN</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>LED_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>NCD0402G1</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Foshan NationStar</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>C130723</t>
@@ -729,51 +808,59 @@
       <c r="I9" s="7" t="n">
         <v>0.0447</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>J1</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>USB-C 16P</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>USB_C_Receptacle_G-Switch_GT-USB-7010ASV</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>GT-USB-7010ASV</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>G-Switch</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>C2988369</t>
         </is>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="10" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="11" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -781,67 +868,77 @@
           <t>J2</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>BAT</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>SolderPad_1.2x2.0mm</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>bare solder pads - no part to order</t>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>R1,R2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>5k1</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>0402WGF5101TCE</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>C25905</t>
         </is>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="11" t="n">
         <v>0.0052</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -849,21 +946,29 @@
           <t>R3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>20k</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF2002TCE</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>C25765</t>
@@ -875,73 +980,89 @@
       <c r="I13" s="7" t="n">
         <v>0.0024</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>0402WGF1001TCE</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>C11702</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="10" t="n">
         <v>0.0039</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="11" t="n">
         <v>0.0039</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>R7,R6</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
+          <t>R6,R7</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>4k7</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF4701TCE</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>C25900</t>
@@ -953,51 +1074,59 @@
       <c r="I15" s="7" t="n">
         <v>0.0058</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>R9,R8</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>R8,R9</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>0402WGF1004TCE</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>C26083</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="11" t="n">
         <v>0.0052</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1005,55 +1134,59 @@
           <t>TP1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>SWDIO</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>bare pad - no part</t>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TP2</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>SWDCLK</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>bare pad - no part</t>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
@@ -1063,55 +1196,59 @@
           <t>TP4</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>GND</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>bare pad - no part</t>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>TP5</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>+3V3</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>bare pad - no part</t>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
@@ -1121,15 +1258,15 @@
           <t>U1</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>ISP1807-LR</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>ISP1807-LR</t>
         </is>
@@ -1139,7 +1276,7 @@
           <t>ISP1807-LR-RS</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Insight SiP</t>
         </is>
@@ -1155,55 +1292,63 @@
       <c r="I21" s="7" t="n">
         <v>12.1151</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Mouser/DigiKey (consign)</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>0 stock at JLC/LCSC - source from Mouser or DigiKey</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>U2</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>LSM6DS3TR-C</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>LGA-14_3x2.5mm_P0.5mm_LayoutBorder3x4y</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>LSM6DS3TR-C</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>C967633</t>
         </is>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="10" t="n">
         <v>1.5538</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="11" t="n">
         <v>1.5538</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1211,21 +1356,29 @@
           <t>U3</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>MCP73831T-2ACI/OT</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MCP73831T-2ACI/OT</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Microchip</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>C424093</t>
@@ -1237,95 +1390,103 @@
       <c r="I23" s="7" t="n">
         <v>0.8596</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>U4</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>TPS7A0533PDBV</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>TPS7A0533PDBVR</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>C493453</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="10" t="n">
         <v>0.2777</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="11" t="n">
         <v>0.2777</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Parts total per board</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="13" t="n">
         <v>15.08</v>
       </c>
     </row>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Ordering notes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Order the PCB and assembly at jlcpcb.com; upload gerbers, BOM and CPL from production/output/.</t>
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Order PCB + assembly at jlcpcb.com with the gerbers, BOM and CPL in production/output/.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>U1 ISP1807-LR-RS is the one exception: 0 stock at JLCPCB/LCSC. Buy it from Mouser or DigiKey and use JLC parts consignment, or hand-place it.</t>
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>U1 ISP1807-LR-RS: 0 stock at JLCPCB/LCSC. Buy from Mouser or DigiKey and consign, or hand-place.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>J2 battery pads and TP1/TP2/TP4/TP5 test pads are bare copper, nothing to order.</t>
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>J2 battery pads and the four test pads are bare copper, nothing to order.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>All passives are 0402 JLC basic parts, no extended-part fee.</t>
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>All passives are 0402 JLC basic parts, no extended-part fee. Prices pulled from the JLCPCB parts API.</t>
         </is>
       </c>
     </row>

--- a/bom/bom-production.xlsx
+++ b/bom/bom-production.xlsx
@@ -522,7 +522,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -628,51 +627,51 @@
       <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>C3,C4</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>C_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>CL05A105KA5NQNC</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>C52923</t>
         </is>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="6" t="n">
         <v>0.012</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.024</v>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -722,51 +721,51 @@
       <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>10u</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>C_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>CGA0402X5R106M6R3GT</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>TDK</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>C23692971</t>
         </is>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="6" t="n">
         <v>0.0244</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.0244</v>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -816,51 +815,51 @@
       <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>J1</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>USB-C 16P</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>USB_C_Receptacle_G-Switch_GT-USB-7010ASV</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>GT-USB-7010ASV</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>G-Switch</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>C2988369</t>
         </is>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="6" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -894,51 +893,51 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>R1,R2</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>5k1</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>0402WGF5101TCE</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>C25905</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="6" t="n">
         <v>0.0026</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.0052</v>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -988,51 +987,51 @@
       <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>0402WGF1001TCE</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>C11702</t>
         </is>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" s="6" t="n">
         <v>0.0039</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="7" t="n">
         <v>0.0039</v>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1082,51 +1081,51 @@
       <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>R8,R9</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>0402WGF1004TCE</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>C26083</t>
         </is>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="6" t="n">
         <v>0.0026</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.0052</v>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1160,31 +1159,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TP2</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>SWDCLK</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
-      <c r="J18" s="9" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>bare pads, nothing to order</t>
         </is>
@@ -1222,31 +1221,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TP5</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>+3V3</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>TestPad_1.0mm</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
-      <c r="J20" s="9" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>bare pads, nothing to order</t>
         </is>
@@ -1304,51 +1303,51 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>U2</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>LSM6DS3TR-C</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>LGA-14_3x2.5mm_P0.5mm_LayoutBorder3x4y</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>LSM6DS3TR-C</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>STMicroelectronics</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>C967633</t>
         </is>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="6" t="n">
         <v>1.5538</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="7" t="n">
         <v>1.5538</v>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1398,51 +1397,51 @@
       <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>U4</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>TPS7A0533PDBV</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>TPS7A0533PDBVR</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Texas Instruments</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>C493453</t>
         </is>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="6" t="n">
         <v>0.2777</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" s="7" t="n">
         <v>0.2777</v>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">

--- a/bom/bom-production.xlsx
+++ b/bom/bom-production.xlsx
@@ -74,7 +74,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -84,11 +84,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00151515"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,10 +115,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -492,20 +483,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="53" customWidth="1" min="11" max="11"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,10 +509,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev 0.3, 11 x 42 mm 4-layer. Exported from KiCad, assembled at JLCPCB with LCSC parts. Quantities per board.</t>
-        </is>
-      </c>
-    </row>
+          <t>v2.1, 13 x 35 mm 4-layer 0.6 mm. Exported from KiCad, assembled at JLCPCB with LCSC parts. Quantities per board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -676,11 +668,11 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>C5,C7,C8,C10</t>
+          <t>C5,C7,C8,C10,C11</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -711,7 +703,7 @@
         <v>0.0055</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.022</v>
+        <v>0.0275</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
@@ -888,14 +880,14 @@
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>bare pads, nothing to order</t>
+          <t>bare solder pads - battery wires solder here, no part to order</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R1,R2</t>
+          <t>LED1,LED2</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -903,54 +895,58 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5k1</t>
+          <t>XL-1010RGBC</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>LED-SMD_4P-L1.0-W1.0-TL_XL-1010RGBC-WS2812B</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>0402WGF5101TCE</t>
+          <t>XL-1010RGBC-2812B</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>XINGLIGHT</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C5349953</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0026</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0052</v>
+        <v>0.1496</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>battery level indicator,bluetooth status indicator</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R1,R2</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>20k</t>
+          <t>5k1</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -960,7 +956,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2002TCE</t>
+          <t>0402WGF5101TCE</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -970,14 +966,14 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>C25765</t>
+          <t>C25905</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.0024</v>
+        <v>0.0026</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.0024</v>
+        <v>0.0052</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
@@ -989,7 +985,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -997,7 +993,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>20k</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1007,7 +1003,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>0402WGF2002TCE</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1017,14 +1013,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25765</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0039</v>
+        <v>0.0024</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0039</v>
+        <v>0.0024</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -1036,15 +1032,15 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>R6,R7</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>4k7</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1054,7 +1050,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0402WGF4701TCE</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1064,14 +1060,14 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>C25900</t>
+          <t>C11702</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.0029</v>
+        <v>0.0039</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0058</v>
+        <v>0.0039</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
@@ -1083,7 +1079,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>R8,R9</t>
+          <t>R6,R7</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>4k7</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1004TCE</t>
+          <t>0402WGF4701TCE</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1111,14 +1107,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>C26083</t>
+          <t>C25900</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0052</v>
+        <v>0.0058</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1130,38 +1126,54 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TP1</t>
+          <t>R8,R9</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>SWDIO</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TestPad_1.0mm</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>bare pads, nothing to order</t>
-        </is>
-      </c>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF1004TCE</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>C26083</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TP2</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1169,30 +1181,50 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>SWDCLK</t>
+          <t>EVQP7C01P</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TestPad_1.0mm</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
+          <t>SW-SMD_EVQP7C01P</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>EVQP7C01P</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PANASONIC</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>C388883</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>bare pads, nothing to order</t>
+          <t>power and pairing button, side actuated</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TP4</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -1200,7 +1232,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>SWDIO</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1223,7 +1255,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TP5</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -1231,7 +1263,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+3V3</t>
+          <t>SWDCLK</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1254,7 +1286,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>TP4</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -1262,50 +1294,30 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>ISP1807-LR</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>ISP1807-LR</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>ISP1807-LR-RS</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Insight SiP</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>C5264268</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>12.1151</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>12.1151</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Mouser/DigiKey (consign)</t>
-        </is>
-      </c>
+          <t>TestPad_1.0mm</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>0 stock at JLC/LCSC - source from Mouser or DigiKey</t>
+          <t>bare pads, nothing to order</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1313,46 +1325,30 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>LSM6DS3TR-C</t>
+          <t>+3V3</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>LGA-14_3x2.5mm_P0.5mm_LayoutBorder3x4y</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>LSM6DS3TR-C</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>STMicroelectronics</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>C967633</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1.5538</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>1.5538</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>JLCPCB</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
+          <t>TestPad_1.0mm</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>bare pads, nothing to order</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -1360,46 +1356,50 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>MCP73831T-2ACI/OT</t>
+          <t>ISP1807-LR</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>BULETM-SMD_ISP1807</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>MCP73831T-2ACI/OT</t>
+          <t>ISP1807-LR-RS</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Microchip</t>
+          <t>Insight SiP</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>C424093</t>
+          <t>C5264268</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.8596</v>
+        <v>12.1151</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.8596</v>
+        <v>12.1151</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>JLCPCB</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr"/>
+          <t>Mouser/DigiKey (consign)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>0 stock at JLC/LCSC - source from Mouser or DigiKey</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -1407,85 +1407,186 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
+          <t>LSM6DS3TR-C</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>LGA-14_3x2.5mm_P0.5mm_LayoutBorder3x4y</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>LSM6DS3TR-C</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>C967633</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>MCP73831T-2ACI/OT</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MCP73831T-2ACI/OT</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Microchip</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>C424093</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
           <t>TPS7A0533PDBV</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>TPS7A0533PDBVR</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Texas Instruments</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>C493453</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H26" s="6" t="n">
         <v>0.2777</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I26" s="7" t="n">
         <v>0.2777</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Parts total per board</t>
         </is>
       </c>
-      <c r="I25" s="13" t="n">
-        <v>15.08</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="I27" s="9" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Ordering notes</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Order PCB + assembly at jlcpcb.com with the gerbers, BOM and CPL in production/output/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Order PCB + assembly at jlcpcb.com with the gerbers, BOM and CPL in production/output/ (regenerate before ordering).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>U1 ISP1807-LR-RS: 0 stock at JLCPCB/LCSC. Buy from Mouser or DigiKey and consign, or hand-place.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>v2.1 additions: LED1/LED2 XL-1010RGBC addressable RGB, SW1 EVQP7C01P side switch, C11 100n.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>J2 battery pads and the four test pads are bare copper, nothing to order.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>All passives are 0402 JLC basic parts, no extended-part fee. Prices pulled from the JLCPCB parts API.</t>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Case: two clear shells via JLCPCB 3D printing (8001 resin); battery 401230 LiPo from Amazon.</t>
         </is>
       </c>
     </row>
